--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2022_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2022_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:22</t>
+    <t xml:space="preserve">2026-09-09 23:18</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2022_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2022_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:18</t>
+    <t xml:space="preserve">2026-09-17 14:14</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2022_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2022_nuble.xlsx
@@ -90,15 +90,15 @@
     <t xml:space="preserve">Ninhue</t>
   </si>
   <si>
+    <t xml:space="preserve">San Ignacio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cobquecura</t>
+  </si>
+  <si>
     <t xml:space="preserve">Portezuelo</t>
   </si>
   <si>
-    <t xml:space="preserve">Cobquecura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Ignacio</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:14</t>
+    <t xml:space="preserve">2026-09-23 12:43</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -844,7 +844,7 @@
         <v>24</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>16205</v>
+        <v>16108</v>
       </c>
       <c r="D20" s="2" t="n">
         <v>2022</v>
@@ -878,7 +878,7 @@
         <v>26</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>16108</v>
+        <v>16205</v>
       </c>
       <c r="D22" s="2" t="n">
         <v>2022</v>

--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2022_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2022_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:43</t>
+    <t xml:space="preserve">2026-10-02 15:04</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2022_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2022_nuble.xlsx
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Ñuble</t>
   </si>
   <si>
-    <t xml:space="preserve">Ranquil</t>
+    <t xml:space="preserve">Ránquil</t>
   </si>
   <si>
     <t xml:space="preserve">Yungay</t>
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 15:04</t>
+    <t xml:space="preserve">2026-10-04 09:14</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2022_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2022_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 09:14</t>
+    <t xml:space="preserve">2026-10-05 11:35</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
